--- a/www/flightdata/xlsx/eoss-322.xlsx
+++ b/www/flightdata/xlsx/eoss-322.xlsx
@@ -3393,7 +3393,7 @@
         <v>28004.41</v>
       </c>
       <c r="I2">
-        <v>593</v>
+        <v>429</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
